--- a/.claude/skills/add-device/templates/devices_template.xlsx
+++ b/.claude/skills/add-device/templates/devices_template.xlsx
@@ -12,6 +12,9 @@
     <sheet name="ModbusRegisters" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="MqttTags" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="OpcuaTags" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="S7Tags" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="HttpTags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="SnmpTags" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -454,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -633,6 +636,64 @@
       <c r="A28" t="inlineStr">
         <is>
           <t>History (all tag sheets): history FALSE = never stored; history_deadband = store only when the value moved more than this. Devices: history_heartbeat_s = store at least this often (default 300).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S7 / HTTP / SNMP (Devices sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>s7: host (+ port 102, rack, slot: S7-1200/1500 0/1, S7-300 0/2, timeout_ms). The CPU must allow PUT/GET and the DBs must not use optimized block access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>http: base_url (https://host[:port][/path]), auth_type none|basic|bearer|header (+ username_env/password_env, token_env, or auth_header + value_env), ca_file_env, verify_tls, timestamp_path/format. Read-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>snmp: host, snmp_version 2c (community_env) or 3 (snmp_user, auth_protocol md5|sha|sha224|sha256|sha384|sha512 + auth_key_env, priv_protocol des|aes128|aes192|aes256 + priv_key_env). Read-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>S7Tags / HttpTags / SnmpTags</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>S7 address: DB1.DBD0 (REAL, DINT, DWORD), DB1.DBW4 (INT, WORD), DB1.DBB6 (BYTE; or 8-byte LREAL/LINT; or STRING + string_length), DB1.DBX6.2 (bit), M10.0, MW20, MD30, I0.1, IW64, Q0.0, QW2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>HTTP: path is appended to base_url (same path = one request per poll), json_path selects the value. SNMP: numeric OID only (1.3.6.1.2.1.33.1.2.4.0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>states (all tag sheets): labels for integer/bool values, e.g. 0=stopped; 1=running. ModbusRegisters: bit + bit_count = multi-bit field (uint16, read-only); encoding bcd = packed decimal digits (uint16 4 digits, uint32 8).</t>
         </is>
       </c>
     </row>
@@ -647,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:BC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -690,6 +751,21 @@
     <col width="9" customWidth="1" min="38" max="38"/>
     <col width="13" customWidth="1" min="39" max="39"/>
     <col width="18" customWidth="1" min="40" max="40"/>
+    <col width="14" customWidth="1" min="41" max="41"/>
+    <col width="14" customWidth="1" min="42" max="42"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
+    <col width="14" customWidth="1" min="44" max="44"/>
+    <col width="14" customWidth="1" min="45" max="45"/>
+    <col width="14" customWidth="1" min="46" max="46"/>
+    <col width="14" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="48" max="48"/>
+    <col width="14" customWidth="1" min="49" max="49"/>
+    <col width="15" customWidth="1" min="50" max="50"/>
+    <col width="14" customWidth="1" min="51" max="51"/>
+    <col width="15" customWidth="1" min="52" max="52"/>
+    <col width="14" customWidth="1" min="53" max="53"/>
+    <col width="15" customWidth="1" min="54" max="54"/>
+    <col width="14" customWidth="1" min="55" max="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -891,6 +967,81 @@
       <c r="AN1" s="4" t="inlineStr">
         <is>
           <t>history_heartbeat_s</t>
+        </is>
+      </c>
+      <c r="AO1" s="4" t="inlineStr">
+        <is>
+          <t>rack</t>
+        </is>
+      </c>
+      <c r="AP1" s="4" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="AQ1" s="4" t="inlineStr">
+        <is>
+          <t>base_url</t>
+        </is>
+      </c>
+      <c r="AR1" s="4" t="inlineStr">
+        <is>
+          <t>auth_header</t>
+        </is>
+      </c>
+      <c r="AS1" s="4" t="inlineStr">
+        <is>
+          <t>token_env</t>
+        </is>
+      </c>
+      <c r="AT1" s="4" t="inlineStr">
+        <is>
+          <t>value_env</t>
+        </is>
+      </c>
+      <c r="AU1" s="4" t="inlineStr">
+        <is>
+          <t>verify_tls</t>
+        </is>
+      </c>
+      <c r="AV1" s="4" t="inlineStr">
+        <is>
+          <t>ca_file_env</t>
+        </is>
+      </c>
+      <c r="AW1" s="4" t="inlineStr">
+        <is>
+          <t>snmp_version</t>
+        </is>
+      </c>
+      <c r="AX1" s="4" t="inlineStr">
+        <is>
+          <t>community_env</t>
+        </is>
+      </c>
+      <c r="AY1" s="4" t="inlineStr">
+        <is>
+          <t>snmp_user</t>
+        </is>
+      </c>
+      <c r="AZ1" s="4" t="inlineStr">
+        <is>
+          <t>auth_protocol</t>
+        </is>
+      </c>
+      <c r="BA1" s="4" t="inlineStr">
+        <is>
+          <t>auth_key_env</t>
+        </is>
+      </c>
+      <c r="BB1" s="4" t="inlineStr">
+        <is>
+          <t>priv_protocol</t>
+        </is>
+      </c>
+      <c r="BC1" s="4" t="inlineStr">
+        <is>
+          <t>priv_key_env</t>
         </is>
       </c>
     </row>
@@ -985,6 +1136,312 @@
       <c r="AL2" s="5" t="n"/>
       <c r="AM2" s="5" t="n"/>
       <c r="AN2" s="5" t="n"/>
+      <c r="AO2" s="5" t="n"/>
+      <c r="AP2" s="5" t="n"/>
+      <c r="AQ2" s="5" t="n"/>
+      <c r="AR2" s="5" t="n"/>
+      <c r="AS2" s="5" t="n"/>
+      <c r="AT2" s="5" t="n"/>
+      <c r="AU2" s="5" t="n"/>
+      <c r="AV2" s="5" t="n"/>
+      <c r="AW2" s="5" t="n"/>
+      <c r="AX2" s="5" t="n"/>
+      <c r="AY2" s="5" t="n"/>
+      <c r="AZ2" s="5" t="n"/>
+      <c r="BA2" s="5" t="n"/>
+      <c r="BB2" s="5" t="n"/>
+      <c r="BC2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t># plc_s7_99</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Example S7-1200 (row ignored)</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>s7</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>kish</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>water_treatment</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>192.168.10.99</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
+      <c r="Q3" s="5" t="n"/>
+      <c r="R3" s="5" t="n"/>
+      <c r="S3" s="5" t="n"/>
+      <c r="T3" s="5" t="n"/>
+      <c r="U3" s="5" t="n"/>
+      <c r="V3" s="5" t="n"/>
+      <c r="W3" s="5" t="n"/>
+      <c r="X3" s="5" t="n"/>
+      <c r="Y3" s="5" t="n"/>
+      <c r="Z3" s="5" t="n"/>
+      <c r="AA3" s="5" t="n"/>
+      <c r="AB3" s="5" t="n"/>
+      <c r="AC3" s="5" t="n"/>
+      <c r="AD3" s="5" t="n"/>
+      <c r="AE3" s="5" t="n"/>
+      <c r="AF3" s="5" t="n"/>
+      <c r="AG3" s="5" t="n"/>
+      <c r="AH3" s="5" t="n"/>
+      <c r="AI3" s="5" t="n"/>
+      <c r="AJ3" s="5" t="n"/>
+      <c r="AK3" s="5" t="n"/>
+      <c r="AL3" s="5" t="n"/>
+      <c r="AM3" s="5" t="n"/>
+      <c r="AN3" s="5" t="n"/>
+      <c r="AO3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" s="5" t="n"/>
+      <c r="AR3" s="5" t="n"/>
+      <c r="AS3" s="5" t="n"/>
+      <c r="AT3" s="5" t="n"/>
+      <c r="AU3" s="5" t="n"/>
+      <c r="AV3" s="5" t="n"/>
+      <c r="AW3" s="5" t="n"/>
+      <c r="AX3" s="5" t="n"/>
+      <c r="AY3" s="5" t="n"/>
+      <c r="AZ3" s="5" t="n"/>
+      <c r="BA3" s="5" t="n"/>
+      <c r="BB3" s="5" t="n"/>
+      <c r="BC3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t># inverter_99</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Example JSON device (row ignored)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>kish</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>solar_roof</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="5" t="n"/>
+      <c r="S4" s="5" t="n"/>
+      <c r="T4" s="5" t="n"/>
+      <c r="U4" s="5" t="n"/>
+      <c r="V4" s="5" t="n"/>
+      <c r="W4" s="5" t="n"/>
+      <c r="X4" s="5" t="n"/>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>bearer</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="n"/>
+      <c r="AA4" s="5" t="n"/>
+      <c r="AB4" s="5" t="n"/>
+      <c r="AC4" s="5" t="n"/>
+      <c r="AD4" s="5" t="n"/>
+      <c r="AE4" s="5" t="n"/>
+      <c r="AF4" s="5" t="n"/>
+      <c r="AG4" s="5" t="n"/>
+      <c r="AH4" s="5" t="n"/>
+      <c r="AI4" s="5" t="n"/>
+      <c r="AJ4" s="5" t="n"/>
+      <c r="AK4" s="5" t="n"/>
+      <c r="AL4" s="5" t="n"/>
+      <c r="AM4" s="5" t="n"/>
+      <c r="AN4" s="5" t="n"/>
+      <c r="AO4" s="5" t="n"/>
+      <c r="AP4" s="5" t="n"/>
+      <c r="AQ4" s="5" t="inlineStr">
+        <is>
+          <t>https://192.168.10.98</t>
+        </is>
+      </c>
+      <c r="AR4" s="5" t="n"/>
+      <c r="AS4" s="5" t="inlineStr">
+        <is>
+          <t>HUB_INVERTER99_TOKEN</t>
+        </is>
+      </c>
+      <c r="AT4" s="5" t="n"/>
+      <c r="AU4" s="5" t="n"/>
+      <c r="AV4" s="5" t="n"/>
+      <c r="AW4" s="5" t="n"/>
+      <c r="AX4" s="5" t="n"/>
+      <c r="AY4" s="5" t="n"/>
+      <c r="AZ4" s="5" t="n"/>
+      <c r="BA4" s="5" t="n"/>
+      <c r="BB4" s="5" t="n"/>
+      <c r="BC4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t># ups_99</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Example SNMPv3 UPS (row ignored)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>snmp</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>kish</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>server_room</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>192.168.10.97</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+      <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="5" t="n"/>
+      <c r="AA5" s="5" t="n"/>
+      <c r="AB5" s="5" t="n"/>
+      <c r="AC5" s="5" t="n"/>
+      <c r="AD5" s="5" t="n"/>
+      <c r="AE5" s="5" t="n"/>
+      <c r="AF5" s="5" t="n"/>
+      <c r="AG5" s="5" t="n"/>
+      <c r="AH5" s="5" t="n"/>
+      <c r="AI5" s="5" t="n"/>
+      <c r="AJ5" s="5" t="n"/>
+      <c r="AK5" s="5" t="n"/>
+      <c r="AL5" s="5" t="n"/>
+      <c r="AM5" s="5" t="n"/>
+      <c r="AN5" s="5" t="n"/>
+      <c r="AO5" s="5" t="n"/>
+      <c r="AP5" s="5" t="n"/>
+      <c r="AQ5" s="5" t="n"/>
+      <c r="AR5" s="5" t="n"/>
+      <c r="AS5" s="5" t="n"/>
+      <c r="AT5" s="5" t="n"/>
+      <c r="AU5" s="5" t="n"/>
+      <c r="AV5" s="5" t="n"/>
+      <c r="AW5" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AX5" s="5" t="n"/>
+      <c r="AY5" s="5" t="inlineStr">
+        <is>
+          <t>hubmon</t>
+        </is>
+      </c>
+      <c r="AZ5" s="5" t="inlineStr">
+        <is>
+          <t>sha256</t>
+        </is>
+      </c>
+      <c r="BA5" s="5" t="inlineStr">
+        <is>
+          <t>HUB_UPS99_AUTH_KEY</t>
+        </is>
+      </c>
+      <c r="BB5" s="5" t="inlineStr">
+        <is>
+          <t>aes128</t>
+        </is>
+      </c>
+      <c r="BC5" s="5" t="inlineStr">
+        <is>
+          <t>HUB_UPS99_PRIV_KEY</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="14">
@@ -1041,7 +1498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1061,6 +1518,9 @@
     <col width="6" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1147,6 +1607,21 @@
       <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>history_deadband</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>bit_count</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>states</t>
         </is>
       </c>
     </row>
@@ -1194,6 +1669,9 @@
       <c r="O2" s="5" t="n"/>
       <c r="P2" s="5" t="n"/>
       <c r="Q2" s="5" t="n"/>
+      <c r="R2" s="5" t="n"/>
+      <c r="S2" s="5" t="n"/>
+      <c r="T2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1251,6 +1729,9 @@
       <c r="O3" s="5" t="n"/>
       <c r="P3" s="5" t="n"/>
       <c r="Q3" s="5" t="n"/>
+      <c r="R3" s="5" t="n"/>
+      <c r="S3" s="5" t="n"/>
+      <c r="T3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1298,6 +1779,65 @@
       </c>
       <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="5" t="n"/>
+      <c r="S4" s="5" t="n"/>
+      <c r="T4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t># meter_99</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>operating_mode</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Bits 4..6 of the status word</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>protocol</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>0=off; 1=auto; 2=manual</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="6">
@@ -1331,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1347,6 +1887,7 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1415,6 +1956,11 @@
           <t>history_deadband</t>
         </is>
       </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -1458,6 +2004,7 @@
       <c r="K2" s="5" t="n"/>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -1481,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1497,6 +2044,7 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1563,6 +2111,11 @@
       <c r="M1" s="4" t="inlineStr">
         <is>
           <t>history_deadband</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>states</t>
         </is>
       </c>
     </row>
@@ -1604,6 +2157,7 @@
       <c r="K2" s="5" t="n"/>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -1619,4 +2173,591 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>device_id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>data_type</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>string_length</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>offset</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>history</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>history_deadband</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t># plc_s7_99</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>inlet_flow</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>m3/h</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>float32</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>DB1.DBD0</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t># plc_s7_99</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>pump_running</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>DB1.DBX6.0</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t># plc_s7_99</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>DB1.DBB7</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>0=stopped; 1=auto; 2=manual</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t># plc_s7_99</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>chlorine_setpoint</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>mg/l</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>float32</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>DB2.DBD0</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>read_write</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>device_id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>data_type</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>path</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>json_path</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>offset</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>history</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>history_deadband</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t># inverter_99</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>ac_power</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>float32</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/status</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>$.ac.power_kw</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>device_id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>data_type</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>oid</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>offset</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>history</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>history_deadband</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t># ups_99</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>battery_charge</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1.3.6.1.2.1.33.1.2.4.0</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t># ups_99</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>battery_status</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>int16</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1.3.6.1.2.1.33.1.2.1.0</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>1=unknown; 2=normal; 3=low; 4=depleted</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>